--- a/test-output/projectResourcesOutputs/GymsDataWithOutPhNum.xlsx
+++ b/test-output/projectResourcesOutputs/GymsDataWithOutPhNum.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
   <si>
     <t>Serial Number</t>
   </si>
@@ -23,49 +23,55 @@
     <t>Gym Phone Number</t>
   </si>
   <si>
-    <t>Sai Dwaraka's Sd Fitness Studio</t>
+    <t>Star Fitness Studio</t>
+  </si>
+  <si>
+    <t>08792071271</t>
+  </si>
+  <si>
+    <t>Iron Forge Gym</t>
+  </si>
+  <si>
+    <t>08867792622</t>
+  </si>
+  <si>
+    <t>Krish's Fitness Pro</t>
+  </si>
+  <si>
+    <t>08296044098</t>
+  </si>
+  <si>
+    <t>Gold's Gym</t>
   </si>
   <si>
     <t>Show Number</t>
   </si>
   <si>
-    <t>Berlin Fitness</t>
-  </si>
-  <si>
-    <t>09008644895</t>
-  </si>
-  <si>
-    <t>Star Fitness Studio</t>
-  </si>
-  <si>
-    <t>08792071271</t>
-  </si>
-  <si>
-    <t>Downsize Slimming And Cosmetic Clinic</t>
-  </si>
-  <si>
-    <t>Gold's Gym</t>
+    <t>Imfit Gym &amp; Crossfit</t>
   </si>
   <si>
     <t>Cult Fit</t>
   </si>
   <si>
+    <t>Abhinav Parkour Academy</t>
+  </si>
+  <si>
+    <t>Vivek Teja's Human Weapon Fitness And Martial Arts</t>
+  </si>
+  <si>
+    <t>09845459437</t>
+  </si>
+  <si>
+    <t>6E GYMS</t>
+  </si>
+  <si>
+    <t>07490833660</t>
+  </si>
+  <si>
     <t>D'Shoolin Functional Strength &amp; therapy</t>
   </si>
   <si>
     <t>08401744248</t>
-  </si>
-  <si>
-    <t>Vivek Teja's Human Weapon Fitness And Martial Arts</t>
-  </si>
-  <si>
-    <t>09845459437</t>
-  </si>
-  <si>
-    <t>Iron Forge Gym</t>
-  </si>
-  <si>
-    <t>08867792622</t>
   </si>
 </sst>
 </file>
@@ -110,7 +116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -165,7 +171,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -173,10 +179,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -184,10 +190,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -195,10 +201,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -221,6 +227,17 @@
       </c>
       <c r="C10" t="s" s="0">
         <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/test-output/projectResourcesOutputs/GymsDataWithOutPhNum.xlsx
+++ b/test-output/projectResourcesOutputs/GymsDataWithOutPhNum.xlsx
@@ -41,37 +41,37 @@
     <t>08296044098</t>
   </si>
   <si>
+    <t>Berlin Fitness</t>
+  </si>
+  <si>
+    <t>09008644895</t>
+  </si>
+  <si>
+    <t>Downsize Slimming And Cosmetic Clinic</t>
+  </si>
+  <si>
+    <t>Show Number</t>
+  </si>
+  <si>
     <t>Gold's Gym</t>
   </si>
   <si>
-    <t>Show Number</t>
-  </si>
-  <si>
-    <t>Imfit Gym &amp; Crossfit</t>
-  </si>
-  <si>
     <t>Cult Fit</t>
   </si>
   <si>
-    <t>Abhinav Parkour Academy</t>
+    <t>Fitness Edge Gym</t>
+  </si>
+  <si>
+    <t>D'Shoolin Functional Strength &amp; therapy</t>
+  </si>
+  <si>
+    <t>08401744248</t>
   </si>
   <si>
     <t>Vivek Teja's Human Weapon Fitness And Martial Arts</t>
   </si>
   <si>
     <t>09845459437</t>
-  </si>
-  <si>
-    <t>6E GYMS</t>
-  </si>
-  <si>
-    <t>07490833660</t>
-  </si>
-  <si>
-    <t>D'Shoolin Functional Strength &amp; therapy</t>
-  </si>
-  <si>
-    <t>08401744248</t>
   </si>
 </sst>
 </file>
@@ -182,7 +182,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -190,10 +190,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -201,10 +201,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -212,10 +212,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
